--- a/media/shoblons/hospital/oth/otd_rep_5.xlsx
+++ b/media/shoblons/hospital/oth/otd_rep_5.xlsx
@@ -5,13 +5,15 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="Лист2" sheetId="2" state="visible" r:id="rId3"/>
     <sheet name="Лист3" sheetId="3" state="visible" r:id="rId4"/>
     <sheet name="Лист4" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="Лист5" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="Лист6" sheetId="6" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="75">
   <si>
     <t xml:space="preserve">Распределение пролеченных больных по нозологическим формам и возрасту</t>
   </si>
@@ -175,6 +177,96 @@
   <si>
     <t xml:space="preserve">Хроническая цереброваскулярная
 Недостаточность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РАСПРЕДЕЛЕНИЕ ВЫБЫВШИХ БОЛЬНЫХ ПО НОЗОЛОГИЧЕСКИМ ФОРМАМ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нозологические формы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пролечено бол-х</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Койко-день</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Средний к/день</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Умерло больных</t>
+  </si>
+  <si>
+    <t xml:space="preserve">экст.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">план.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Парехиматозное кровоизлияние</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПНМК</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ХЦВК,декомп.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ИТОГО</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РАСПРЕДЕЛЕНИЕ УМЕРШИХ БОЛЬНЫХ ПО НОЗОЛОГИЧЕСКИМ ФОРМАМ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Умерло
+Всего</t>
+  </si>
+  <si>
+    <t xml:space="preserve">К/день
+Общий</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сред.
+к/дн.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Длительность нахождения (дн.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">До 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 — 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 — 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 — 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 и &gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РАСПРЕДЕЛЕНИЕ УМЕРШИХ БОЛЬНЫХ ПО НОЗОЛОГИЧЕСКИМ ФОРМАМ И ВОЗРАСТУ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 — 29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 — 49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 — 59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 — 69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70 — 79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80 и старше</t>
   </si>
 </sst>
 </file>
@@ -184,7 +276,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -205,11 +297,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -261,7 +348,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -286,6 +373,10 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -298,12 +389,16 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -324,7 +419,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:N17"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.19"/>
@@ -501,7 +596,7 @@
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
+      <c r="N9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
@@ -521,7 +616,7 @@
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
+      <c r="N10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
@@ -541,10 +636,10 @@
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
+      <c r="N11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -561,7 +656,7 @@
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
+      <c r="N12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
@@ -581,7 +676,7 @@
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
+      <c r="N13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
@@ -601,7 +696,7 @@
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
+      <c r="N14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
@@ -621,13 +716,13 @@
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
+      <c r="N15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="6"/>
+      <c r="B16" s="7"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -639,13 +734,13 @@
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
+      <c r="N16" s="7"/>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="6"/>
+      <c r="B17" s="7"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -657,7 +752,7 @@
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
+      <c r="N17" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -687,10 +782,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:Z18"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="5.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="5.1"/>
@@ -776,7 +871,9 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -1024,7 +1121,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -1056,7 +1153,7 @@
       <c r="Z10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -1120,7 +1217,7 @@
       <c r="Z12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>41</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -1184,7 +1281,7 @@
       <c r="Z14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -1216,7 +1313,7 @@
       <c r="Z15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="8" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -1251,7 +1348,7 @@
       <c r="A17" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="6"/>
+      <c r="B17" s="7"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -1281,7 +1378,7 @@
       <c r="A18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="6"/>
+      <c r="B18" s="7"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -1346,34 +1443,34 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:R17"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="36.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="4" style="0" width="6.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="8.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="10.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="10.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="8.47"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1"/>
@@ -1392,7 +1489,9 @@
       <c r="N3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -1504,7 +1603,7 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="5" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="4" t="s">
@@ -1565,7 +1664,7 @@
       <c r="N11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -1648,7 +1747,7 @@
       <c r="A16" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="6"/>
+      <c r="B16" s="7"/>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
       <c r="E16" s="6"/>
@@ -1666,7 +1765,7 @@
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="6"/>
+      <c r="B17" s="7"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -1708,10 +1807,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:Z18"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="5.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="5.1"/>
@@ -1797,7 +1896,9 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -2045,7 +2146,7 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>18</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -2077,7 +2178,7 @@
       <c r="Z10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="8" t="s">
         <v>20</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -2141,7 +2242,7 @@
       <c r="Z12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="8" t="s">
         <v>41</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -2205,7 +2306,7 @@
       <c r="Z14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="8" t="s">
         <v>28</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -2237,7 +2338,7 @@
       <c r="Z15" s="6"/>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="8" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -2272,7 +2373,7 @@
       <c r="A17" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="6"/>
+      <c r="B17" s="7"/>
       <c r="C17" s="6"/>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -2302,7 +2403,7 @@
       <c r="A18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="6"/>
+      <c r="B18" s="7"/>
       <c r="C18" s="6"/>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
@@ -2359,4 +2460,459 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A2:M11"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="2" style="0" width="8.16"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="K3:M3"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.39375" right="0.39375" top="0.7875" bottom="1.05277777777778" header="0.511811023622047" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A2:I17"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.34"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="A12:H12"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.39375" right="0.39375" top="0.7875" bottom="1.05277777777778" header="0.511811023622047" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Times New Roman,Обычный"&amp;12Страница &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>